--- a/Docs/Upgrades.xlsx
+++ b/Docs/Upgrades.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
   <si>
     <t>Shopkeeper</t>
   </si>
@@ -258,9 +258,6 @@
     <t>Flashbacks</t>
   </si>
   <si>
-    <t>The new scars weigh down all the limbs. This unit's attack damage is decreased by 1 (To a minimum of 0)</t>
-  </si>
-  <si>
     <t>The soldier makes full recovery, but the sircumstances of the injury break their spirit. This unit gains "Paranoid"</t>
   </si>
   <si>
@@ -273,7 +270,16 @@
     <t>Delayed wounds</t>
   </si>
   <si>
-    <t>The soldier gets away with a scratch… This time. This unit gains "Tender"</t>
+    <t>Tremors</t>
+  </si>
+  <si>
+    <t>The soldier avoids lethal injuries, but their grip strength and steadiness is not the same. This unit gains "Slow-Handed"</t>
+  </si>
+  <si>
+    <t>The soldier makes a recovery… This time. This unit gains "Tender"</t>
+  </si>
+  <si>
+    <t>The new scars weigh the soldier down. This unit's attack damage is decreased by 1 (To a minimum of 0)</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F26"/>
+  <dimension ref="B1:F27"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="18"/>
@@ -1494,7 +1500,7 @@
         <v>64</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1519,7 +1525,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="22">
         <v>10</v>
       </c>
@@ -1546,10 +1552,10 @@
         <v>12</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1557,10 +1563,10 @@
         <v>13</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1568,10 +1574,10 @@
         <v>14</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1579,10 +1585,10 @@
         <v>15</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1590,10 +1596,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1601,10 +1607,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1612,10 +1618,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1623,10 +1629,10 @@
         <v>19</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1634,10 +1640,10 @@
         <v>20</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1645,10 +1651,10 @@
         <v>21</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1656,10 +1662,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="4:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1667,20 +1673,31 @@
         <v>23</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" ht="30" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D26" s="22">
         <v>24</v>
       </c>
       <c r="E26" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="4:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="D27" s="22">
+        <v>25</v>
+      </c>
+      <c r="E27" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F27" s="15" t="s">
         <v>72</v>
       </c>
     </row>
